--- a/stories/arbres/TREE-SAN-017.xlsx
+++ b/stories/arbres/TREE-SAN-017.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Lina se réveille. Maman l'appelle à table. Dans l'assiette, il y a un légume. Maman dit : tu peux goûter. Une petite portion. Puis tu nommes le goût. Lina s'assoit.</t>
+          <t>Lina se réveille. Maman l'appelle à table. Dans l'assiette, il y a un légume. Tu peux goûter. Une petite portion. Puis tu nommes le goût. Lina s'assoit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Lina se réveille. Maman l'appelle à table. Dans l'assiette, il y a un légume.
+maman|Tu peux goûter.
+narrateur|Une petite portion. Puis tu nommes le goût. Lina s'assoit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1515,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, la table du salon, ou le jardin.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1653,6 +1682,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers la cuisine. Ça sent la soupe. maman est tout près. Lina goûte une petite portion. Lina goûte une petite portion. Elle nomme le goût. maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1867,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Lina prend une petite bouchée. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2040,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Lina a retenu. Lina goûte une petite portion. Elle nomme le goût. On continue avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2191,6 +2235,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la carotte, le petit pois, ou la courgette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2353,6 +2402,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi la carotte. La carotte croque. maman montre lentement. Lina nomme le goût. Lina goûte une petite portion. Elle nomme le goût. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2543,6 +2597,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre doux, sucré, ou tiède.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2705,6 +2764,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint doux. Maman sourit. Lina goûte une petite portion. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la cuisine, puis la carotte.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2867,6 +2931,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3029,6 +3098,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint sucré. Papa est près. Lina nomme le goût. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la cuisine, puis la carotte.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3191,6 +3265,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3353,6 +3432,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint tiède. L'eau est dans le verre. Lina prend une petite bouchée. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la cuisine, puis la carotte.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3515,6 +3599,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3677,6 +3766,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le petit pois. Le pois est rond. maman montre lentement. Lina prend une petite bouchée. Lina goûte une petite portion. Elle nomme le goût. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3867,6 +3961,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre doux, sucré, ou tiède.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4029,6 +4128,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint doux. Papa est près. Lina nomme le goût. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la cuisine, puis le petit pois.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4191,6 +4295,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4353,6 +4462,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint sucré. L'eau est dans le verre. Lina prend une petite bouchée. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la cuisine, puis le petit pois.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4515,6 +4629,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4677,6 +4796,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint tiède. Une feuille tombe. Lina dit le goût à maman. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la cuisine, puis le petit pois.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4839,6 +4963,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5001,6 +5130,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi la courgette. La courgette est tendre. maman montre lentement. Lina dit le goût à maman. Lina goûte une petite portion. Elle nomme le goût. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5191,6 +5325,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre doux, sucré, ou tiède.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5353,6 +5492,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint doux. L'eau est dans le verre. Lina prend une petite bouchée. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la cuisine, puis la courgette.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5515,6 +5659,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5677,6 +5826,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint sucré. Une feuille tombe. Lina dit le goût à maman. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la cuisine, puis la courgette.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5839,6 +5993,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6001,6 +6160,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint tiède. Il y a des miettes. Lina laisse le reste dans l'assiette. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la cuisine, puis la courgette.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6163,6 +6327,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6325,6 +6494,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers la table du salon. La table est lisse. maman est tout près. Lina nomme le goût. Lina goûte une petite portion. Elle nomme le goût. maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6507,6 +6681,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Lina prend une petite bouchée. Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6531,7 +6710,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Lina respire. Lina goûte une petite portion. Elle nomme le goût. maman dit : je suis là.</t>
+          <t>Lina respire. Lina goûte une petite portion. Elle nomme le goût. Je suis là.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6673,6 +6852,12 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Lina respire. Lina goûte une petite portion. Elle nomme le goût.
+maman|Je suis là.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6863,6 +7048,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la carotte, le petit pois, ou la courgette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7025,6 +7215,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi la carotte. Maman sourit. maman montre lentement. Lina prend une petite bouchée. Lina goûte une petite portion. Elle nomme le goût. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7215,6 +7410,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre doux, sucré, ou tiède.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7377,6 +7577,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint doux. Papa est près. Lina goûte une petite portion. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la table du salon, puis la carotte.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7539,6 +7744,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7701,6 +7911,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint sucré. L'eau est dans le verre. Lina nomme le goût. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la table du salon, puis la carotte.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7863,6 +8078,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8025,6 +8245,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint tiède. Une feuille tombe. Lina prend une petite bouchée. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la table du salon, puis la carotte.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8187,6 +8412,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8349,6 +8579,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le petit pois. Papa est près. maman montre lentement. Lina dit le goût à maman. Lina goûte une petite portion. Elle nomme le goût. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8539,6 +8774,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre doux, sucré, ou tiède.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8701,6 +8941,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint doux. L'eau est dans le verre. Lina nomme le goût. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la table du salon, puis le petit pois.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8863,6 +9108,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9025,6 +9275,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint sucré. Une feuille tombe. Lina prend une petite bouchée. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la table du salon, puis le petit pois.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9187,6 +9442,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9349,6 +9609,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint tiède. Il y a des miettes. Lina dit le goût à maman. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la table du salon, puis le petit pois.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9511,6 +9776,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9673,6 +9943,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi la courgette. L'eau est dans le verre. maman montre lentement. Lina laisse le reste dans l'assiette. Lina goûte une petite portion. Elle nomme le goût. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9863,6 +10138,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre doux, sucré, ou tiède.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10025,6 +10305,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint doux. Une feuille tombe. Lina prend une petite bouchée. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la table du salon, puis la courgette.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10187,6 +10472,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10349,6 +10639,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint sucré. Il y a des miettes. Lina dit le goût à maman. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la table du salon, puis la courgette.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10511,6 +10806,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10673,6 +10973,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint tiède. Le bol est tiède. Lina laisse le reste dans l'assiette. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la table du salon, puis la courgette.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10835,6 +11140,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10997,6 +11307,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers le jardin. Le soleil est chaud. maman est tout près. Lina prend une petite bouchée. Lina goûte une petite portion. Elle nomme le goût. maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11177,6 +11492,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Lina prend une petite bouchée. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -11345,6 +11665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|C'est juste. Lina goûte une petite portion. Elle nomme le goût. Lina donne la main à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11535,6 +11860,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la carotte, le petit pois, ou la courgette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11697,6 +12027,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi la carotte. Une feuille tombe. maman montre lentement. Lina dit le goût à maman. Lina goûte une petite portion. Elle nomme le goût. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11887,6 +12222,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre doux, sucré, ou tiède.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12049,6 +12389,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint doux. L'eau est dans le verre. Lina goûte une petite portion. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. le jardin, puis la carotte.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12211,6 +12556,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12373,6 +12723,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint sucré. Une feuille tombe. Lina nomme le goût. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. le jardin, puis la carotte.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12535,6 +12890,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12697,6 +13057,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint tiède. Il y a des miettes. Lina prend une petite bouchée. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. le jardin, puis la carotte.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12859,6 +13224,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13021,6 +13391,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le petit pois. Il y a des miettes. maman montre lentement. Lina laisse le reste dans l'assiette. Lina goûte une petite portion. Elle nomme le goût. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13211,6 +13586,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre doux, sucré, ou tiède.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13373,6 +13753,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint doux. Une feuille tombe. Lina nomme le goût. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. le jardin, puis le petit pois.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13535,6 +13920,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13697,6 +14087,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint sucré. Il y a des miettes. Lina prend une petite bouchée. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. le jardin, puis le petit pois.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13859,6 +14254,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14021,6 +14421,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint tiède. Le bol est tiède. Lina dit le goût à maman. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. le jardin, puis le petit pois.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14183,6 +14588,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14345,6 +14755,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi la courgette. Le bol est tiède. maman montre lentement. Lina goûte une petite portion. Lina goûte une petite portion. Elle nomme le goût. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14535,6 +14950,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre doux, sucré, ou tiède.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14697,6 +15117,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint doux. Il y a des miettes. Lina prend une petite bouchée. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. le jardin, puis la courgette.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14859,6 +15284,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15021,6 +15451,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint sucré. Le bol est tiède. Lina dit le goût à maman. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. le jardin, puis la courgette.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15183,6 +15618,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15345,6 +15785,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint tiède. Ça sent la soupe. Lina laisse le reste dans l'assiette. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. le jardin, puis la courgette.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15507,6 +15952,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15525,7 +15975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15542,6 +15992,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SAN-017.xlsx
+++ b/stories/arbres/TREE-SAN-017.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Une petite portion. Puis tu nommes le goût. Lina s'assoit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1520,6 +1526,7 @@
           <t>narrateur|On peut prendre la cuisine, la table du salon, ou le jardin.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1687,6 +1694,7 @@
           <t>narrateur|Lina va vers la cuisine. Ça sent la soupe. maman est tout près. Lina goûte une petite portion. Lina goûte une petite portion. Elle nomme le goût. maman sourit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1874,6 +1882,7 @@
           <t>narrateur|Lina prend une petite bouchée. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2045,6 +2054,7 @@
           <t>narrateur|Oui. Lina a retenu. Lina goûte une petite portion. Elle nomme le goût. On continue avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2240,6 +2250,7 @@
           <t>narrateur|On peut prendre la carotte, le petit pois, ou la courgette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2407,6 +2418,7 @@
           <t>narrateur|Lina a choisi la carotte. La carotte croque. maman montre lentement. Lina nomme le goût. Lina goûte une petite portion. Elle nomme le goût. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2602,6 +2614,7 @@
           <t>narrateur|On peut prendre doux, sucré, ou tiède.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2769,6 +2782,7 @@
           <t>narrateur|Lina rejoint doux. Maman sourit. Lina goûte une petite portion. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la cuisine, puis la carotte.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2936,6 +2950,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3103,6 +3118,7 @@
           <t>narrateur|Lina rejoint sucré. Papa est près. Lina nomme le goût. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la cuisine, puis la carotte.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3270,6 +3286,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3437,6 +3454,7 @@
           <t>narrateur|Lina rejoint tiède. L'eau est dans le verre. Lina prend une petite bouchée. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la cuisine, puis la carotte.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3604,6 +3622,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3771,6 +3790,7 @@
           <t>narrateur|Lina a choisi le petit pois. Le pois est rond. maman montre lentement. Lina prend une petite bouchée. Lina goûte une petite portion. Elle nomme le goût. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3966,6 +3986,7 @@
           <t>narrateur|On peut prendre doux, sucré, ou tiède.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4133,6 +4154,7 @@
           <t>narrateur|Lina rejoint doux. Papa est près. Lina nomme le goût. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la cuisine, puis le petit pois.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4300,6 +4322,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4467,6 +4490,7 @@
           <t>narrateur|Lina rejoint sucré. L'eau est dans le verre. Lina prend une petite bouchée. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la cuisine, puis le petit pois.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4634,6 +4658,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4801,6 +4826,7 @@
           <t>narrateur|Lina rejoint tiède. Une feuille tombe. Lina dit le goût à maman. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la cuisine, puis le petit pois.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4968,6 +4994,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5135,6 +5162,7 @@
           <t>narrateur|Lina a choisi la courgette. La courgette est tendre. maman montre lentement. Lina dit le goût à maman. Lina goûte une petite portion. Elle nomme le goût. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5330,6 +5358,7 @@
           <t>narrateur|On peut prendre doux, sucré, ou tiède.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5497,6 +5526,7 @@
           <t>narrateur|Lina rejoint doux. L'eau est dans le verre. Lina prend une petite bouchée. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la cuisine, puis la courgette.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5664,6 +5694,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5831,6 +5862,7 @@
           <t>narrateur|Lina rejoint sucré. Une feuille tombe. Lina dit le goût à maman. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la cuisine, puis la courgette.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5998,6 +6030,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6165,6 +6198,7 @@
           <t>narrateur|Lina rejoint tiède. Il y a des miettes. Lina laisse le reste dans l'assiette. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la cuisine, puis la courgette.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6332,6 +6366,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6499,6 +6534,7 @@
           <t>narrateur|Lina va vers la table du salon. La table est lisse. maman est tout près. Lina nomme le goût. Lina goûte une petite portion. Elle nomme le goût. maman sourit.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6686,6 +6722,7 @@
           <t>narrateur|Lina prend une petite bouchée. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6858,6 +6895,7 @@
 maman|Je suis là.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7053,6 +7091,7 @@
           <t>narrateur|On peut prendre la carotte, le petit pois, ou la courgette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7220,6 +7259,7 @@
           <t>narrateur|Lina a choisi la carotte. Maman sourit. maman montre lentement. Lina prend une petite bouchée. Lina goûte une petite portion. Elle nomme le goût. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7415,6 +7455,7 @@
           <t>narrateur|On peut prendre doux, sucré, ou tiède.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7582,6 +7623,7 @@
           <t>narrateur|Lina rejoint doux. Papa est près. Lina goûte une petite portion. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la table du salon, puis la carotte.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7749,6 +7791,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7916,6 +7959,7 @@
           <t>narrateur|Lina rejoint sucré. L'eau est dans le verre. Lina nomme le goût. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la table du salon, puis la carotte.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8083,6 +8127,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8250,6 +8295,7 @@
           <t>narrateur|Lina rejoint tiède. Une feuille tombe. Lina prend une petite bouchée. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la table du salon, puis la carotte.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8417,6 +8463,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8584,6 +8631,7 @@
           <t>narrateur|Lina a choisi le petit pois. Papa est près. maman montre lentement. Lina dit le goût à maman. Lina goûte une petite portion. Elle nomme le goût. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8779,6 +8827,7 @@
           <t>narrateur|On peut prendre doux, sucré, ou tiède.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8946,6 +8995,7 @@
           <t>narrateur|Lina rejoint doux. L'eau est dans le verre. Lina nomme le goût. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la table du salon, puis le petit pois.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9113,6 +9163,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9280,6 +9331,7 @@
           <t>narrateur|Lina rejoint sucré. Une feuille tombe. Lina prend une petite bouchée. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la table du salon, puis le petit pois.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9447,6 +9499,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9614,6 +9667,7 @@
           <t>narrateur|Lina rejoint tiède. Il y a des miettes. Lina dit le goût à maman. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la table du salon, puis le petit pois.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9781,6 +9835,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9948,6 +10003,7 @@
           <t>narrateur|Lina a choisi la courgette. L'eau est dans le verre. maman montre lentement. Lina laisse le reste dans l'assiette. Lina goûte une petite portion. Elle nomme le goût. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10143,6 +10199,7 @@
           <t>narrateur|On peut prendre doux, sucré, ou tiède.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10310,6 +10367,7 @@
           <t>narrateur|Lina rejoint doux. Une feuille tombe. Lina prend une petite bouchée. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la table du salon, puis la courgette.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10477,6 +10535,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10644,6 +10703,7 @@
           <t>narrateur|Lina rejoint sucré. Il y a des miettes. Lina dit le goût à maman. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la table du salon, puis la courgette.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10811,6 +10871,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10978,6 +11039,7 @@
           <t>narrateur|Lina rejoint tiède. Le bol est tiède. Lina laisse le reste dans l'assiette. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. la table du salon, puis la courgette.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11145,6 +11207,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11312,6 +11375,7 @@
           <t>narrateur|Lina va vers le jardin. Le soleil est chaud. maman est tout près. Lina prend une petite bouchée. Lina goûte une petite portion. Elle nomme le goût. maman sourit.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11499,6 +11563,7 @@
           <t>narrateur|Lina prend une petite bouchée. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11670,6 +11735,7 @@
           <t>narrateur|C'est juste. Lina goûte une petite portion. Elle nomme le goût. Lina donne la main à maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11865,6 +11931,7 @@
           <t>narrateur|On peut prendre la carotte, le petit pois, ou la courgette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12032,6 +12099,7 @@
           <t>narrateur|Lina a choisi la carotte. Une feuille tombe. maman montre lentement. Lina dit le goût à maman. Lina goûte une petite portion. Elle nomme le goût. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12227,6 +12295,7 @@
           <t>narrateur|On peut prendre doux, sucré, ou tiède.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12394,6 +12463,7 @@
           <t>narrateur|Lina rejoint doux. L'eau est dans le verre. Lina goûte une petite portion. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. le jardin, puis la carotte.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12561,6 +12631,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12728,6 +12799,7 @@
           <t>narrateur|Lina rejoint sucré. Une feuille tombe. Lina nomme le goût. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. le jardin, puis la carotte.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12895,6 +12967,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13062,6 +13135,7 @@
           <t>narrateur|Lina rejoint tiède. Il y a des miettes. Lina prend une petite bouchée. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. le jardin, puis la carotte.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13229,6 +13303,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13396,6 +13471,7 @@
           <t>narrateur|Lina a choisi le petit pois. Il y a des miettes. maman montre lentement. Lina laisse le reste dans l'assiette. Lina goûte une petite portion. Elle nomme le goût. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13591,6 +13667,7 @@
           <t>narrateur|On peut prendre doux, sucré, ou tiède.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13758,6 +13835,7 @@
           <t>narrateur|Lina rejoint doux. Une feuille tombe. Lina nomme le goût. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. le jardin, puis le petit pois.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13925,6 +14003,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14092,6 +14171,7 @@
           <t>narrateur|Lina rejoint sucré. Il y a des miettes. Lina prend une petite bouchée. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. le jardin, puis le petit pois.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14259,6 +14339,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14426,6 +14507,7 @@
           <t>narrateur|Lina rejoint tiède. Le bol est tiède. Lina dit le goût à maman. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. le jardin, puis le petit pois.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14593,6 +14675,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14760,6 +14843,7 @@
           <t>narrateur|Lina a choisi la courgette. Le bol est tiède. maman montre lentement. Lina goûte une petite portion. Lina goûte une petite portion. Elle nomme le goût. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14955,6 +15039,7 @@
           <t>narrateur|On peut prendre doux, sucré, ou tiède.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15122,6 +15207,7 @@
           <t>narrateur|Lina rejoint doux. Il y a des miettes. Lina prend une petite bouchée. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. le jardin, puis la courgette.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15289,6 +15375,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15456,6 +15543,7 @@
           <t>narrateur|Lina rejoint sucré. Le bol est tiède. Lina dit le goût à maman. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. le jardin, puis la courgette.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15623,6 +15711,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15790,6 +15879,7 @@
           <t>narrateur|Lina rejoint tiède. Ça sent la soupe. Lina laisse le reste dans l'assiette. Lina goûte une petite portion. Elle nomme le goût. maman dit merci. le jardin, puis la courgette.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15957,6 +16047,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15975,7 +16066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15999,6 +16090,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16013,7 +16118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16200,6 +16305,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
